--- a/Analyzer解析管理.xlsx
+++ b/Analyzer解析管理.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://b0aa600df9934664bf4b-my.sharepoint.com/personal/masaharu_itou_ab_east_ntt_co_jp/Documents/ドキュメント/GitHub/SOSDB_Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25292" documentId="8_{F7BFCF04-A82A-4CEF-B166-E6043107DC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9790FC63-A25E-4AFE-A673-AD550DF6C7BB}"/>
+  <xr:revisionPtr revIDLastSave="29689" documentId="8_{F7BFCF04-A82A-4CEF-B166-E6043107DC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90FB10C5-FAB9-4019-8592-00988AF1DFE5}"/>
   <bookViews>
-    <workbookView xWindow="5625" yWindow="1710" windowWidth="19740" windowHeight="13425" xr2:uid="{9A52E20E-468D-4D4B-A7CD-66A9B60B5C6C}"/>
+    <workbookView xWindow="975" yWindow="975" windowWidth="24000" windowHeight="12000" activeTab="2" xr2:uid="{9A52E20E-468D-4D4B-A7CD-66A9B60B5C6C}"/>
   </bookViews>
   <sheets>
     <sheet name="PathChartTree" sheetId="5" r:id="rId1"/>
     <sheet name="PathChart" sheetId="4" r:id="rId2"/>
     <sheet name="関数トレース" sheetId="2" r:id="rId3"/>
     <sheet name="ProcList" sheetId="1" r:id="rId4"/>
-    <sheet name="関数依存関係" sheetId="11" r:id="rId5"/>
+    <sheet name="関数依存関係" sheetId="12" r:id="rId5"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId6"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3028" uniqueCount="983">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="987">
   <si>
     <t>Module</t>
   </si>
@@ -2340,78 +2340,6 @@
   </si>
   <si>
     <t>ParentProcedure</t>
-  </si>
-  <si>
-    <t>CreatePathChart_V3 &lt;modPathChart&gt;</t>
-  </si>
-  <si>
-    <t>│パスチャート作成</t>
-  </si>
-  <si>
-    <t>│　　　タイムスタンプ取得</t>
-  </si>
-  <si>
-    <t>├─　ClearChartShapes &lt;modPathChart&gt;</t>
-  </si>
-  <si>
-    <t>│　　　チャート初期化</t>
-  </si>
-  <si>
-    <t>├─　GetBranchSize &lt;modPathChart&gt;</t>
-  </si>
-  <si>
-    <t>│　　　分岐サイズ取得</t>
-  </si>
-  <si>
-    <t>├─　BuildCaptionText &lt;modPathChart&gt;</t>
-  </si>
-  <si>
-    <t>│　　│ノード表示文字列生成</t>
-  </si>
-  <si>
-    <t>│　　　　　　関数情報取得</t>
-  </si>
-  <si>
-    <t>├─　DrawNode &lt;modPathChart&gt;</t>
-  </si>
-  <si>
-    <t>│　　　ノード作成</t>
-  </si>
-  <si>
-    <t>├─　ExportPathChartToPowerPoint &lt;modPathChart&gt;</t>
-  </si>
-  <si>
-    <t>│　　　PowerPoint出力</t>
-  </si>
-  <si>
-    <t>│　　│PNG出力</t>
-  </si>
-  <si>
-    <t>│　　├─　GetChartRange &lt;modPathChart&gt;</t>
-  </si>
-  <si>
-    <t>│　　│　　　チャート範囲取得</t>
-  </si>
-  <si>
-    <t>│　　　　　　出力フォルダ取得</t>
-  </si>
-  <si>
-    <t>├─　ExportPathChartToText &lt;modPathChartText&gt;</t>
-  </si>
-  <si>
-    <t>│　　│テキストチャート出力</t>
-  </si>
-  <si>
-    <t>│　　└─　OutputTreeNodeList &lt;modPathChartText&gt;</t>
-  </si>
-  <si>
-    <t>│　　　　　　ツリー一覧出力</t>
-  </si>
-  <si>
-    <t>└─　GetChartRange &lt;modPathChart&gt;</t>
-  </si>
-  <si>
-    <t>　　　　チャート範囲取得</t>
   </si>
   <si>
     <t>OneDrive配下のGitHub管理フォルダを_x000D_
@@ -3110,30 +3038,9 @@
     <t>modToolManager</t>
   </si>
   <si>
-    <t>RestoreAnalyzerBook</t>
-  </si>
-  <si>
-    <t>解析ツール復元</t>
-  </si>
-  <si>
-    <t>非表示中の解析ツール画面を復元する</t>
-  </si>
-  <si>
-    <t>MainMenu、ソース管理、_x000D_
-関数管理画面終了時に呼び出す_x000D_
-解析ツールブックを再表示し_x000D_
-Mainシートをアクティブにする</t>
-  </si>
-  <si>
-    <t>Public Sub RestoreAnalyzerBook()</t>
-  </si>
-  <si>
     <t>modPathChartCommon</t>
   </si>
   <si>
-    <t>メインメニュー終了制御</t>
-  </si>
-  <si>
     <t>"SetIssueToUI=" &amp; GetBranchSize("SetIssueToUI")</t>
   </si>
   <si>
@@ -3143,16 +3050,119 @@
     <t>"Get_MonshinInfo=" &amp; GetBranchSize("Get_MonshinInfo")</t>
   </si>
   <si>
+    <t>SaveMainWindowState</t>
+  </si>
+  <si>
+    <t>起動時Window保存</t>
+  </si>
+  <si>
+    <t>起動時のExcel Window位置と_x000D_
+サイズを保存する</t>
+  </si>
+  <si>
+    <t>Public Sub SaveMainWindowState()</t>
+  </si>
+  <si>
+    <t>RestoreMainWindowState</t>
+  </si>
+  <si>
+    <t>Public Sub RestoreMainWindowState()</t>
+  </si>
+  <si>
+    <t>ResizeMainWindow</t>
+  </si>
+  <si>
+    <t>Public Sub ResizeMainWindow()</t>
+  </si>
+  <si>
+    <t>ResizeManageWindow</t>
+  </si>
+  <si>
+    <t>Public Sub ResizeManageWindow( _</t>
+  </si>
+  <si>
+    <t>CreatePathChart_V3 &lt;modPathChart&gt;</t>
+  </si>
+  <si>
+    <t>│パスチャート作成</t>
+  </si>
+  <si>
     <t>├─　GetTimeStamp &lt;modPowerPointChart&gt;</t>
   </si>
   <si>
+    <t>│　　　タイムスタンプ取得</t>
+  </si>
+  <si>
+    <t>├─　ClearChartShapes &lt;modPathChart&gt;</t>
+  </si>
+  <si>
+    <t>│　　　チャート初期化</t>
+  </si>
+  <si>
+    <t>├─　GetBranchSize &lt;modPathChart&gt;</t>
+  </si>
+  <si>
+    <t>│　　　分岐サイズ取得</t>
+  </si>
+  <si>
+    <t>├─　BuildCaptionText &lt;modPathChart&gt;</t>
+  </si>
+  <si>
+    <t>│　　│ノード表示文字列生成</t>
+  </si>
+  <si>
     <t>│　　└─　GetProcInfo &lt;modAnalyzerCommon&gt;</t>
   </si>
   <si>
+    <t>│　　　　　　関数情報取得</t>
+  </si>
+  <si>
+    <t>├─　DrawNode &lt;modPathChart&gt;</t>
+  </si>
+  <si>
+    <t>│　　　ノード作成</t>
+  </si>
+  <si>
+    <t>├─　ExportPathChartToPowerPoint &lt;modPathChart&gt;</t>
+  </si>
+  <si>
+    <t>│　　　PowerPoint出力</t>
+  </si>
+  <si>
     <t>├─　ExportPathChartToPNG &lt;modPowerPointChart&gt;</t>
   </si>
   <si>
+    <t>│　　│PNG出力</t>
+  </si>
+  <si>
+    <t>│　　├─　GetChartRange &lt;modPathChart&gt;</t>
+  </si>
+  <si>
+    <t>│　　│　　　チャート範囲取得</t>
+  </si>
+  <si>
     <t>│　　└─　GetOutputFolder &lt;modPowerPointChart&gt;</t>
+  </si>
+  <si>
+    <t>│　　　　　　出力フォルダ取得</t>
+  </si>
+  <si>
+    <t>├─　ExportPathChartToText &lt;modPathChartText&gt;</t>
+  </si>
+  <si>
+    <t>│　　│テキストチャート出力</t>
+  </si>
+  <si>
+    <t>│　　└─　OutputTreeNodeList &lt;modPathChartText&gt;</t>
+  </si>
+  <si>
+    <t>│　　　　　　ツリー一覧出力</t>
+  </si>
+  <si>
+    <t>└─　GetChartRange &lt;modPathChart&gt;</t>
+  </si>
+  <si>
+    <t>　　　　チャート範囲取得</t>
   </si>
 </sst>
 </file>
@@ -3288,35 +3298,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -3363,22 +3345,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>3175</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>241300</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="N_000001">
+        <xdr:cNvPr id="2" name="N_000001">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C36913F-0AF4-56D0-5DEF-FA47188C8C42}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18ABA006-02D6-733D-BF0D-974396A62E76}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3393,11 +3375,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
+          <a:srgbClr val="5DBAFF"/>
         </a:solidFill>
-        <a:ln w="38100">
+        <a:ln w="15875">
           <a:solidFill>
-            <a:srgbClr val="0070C0"/>
+            <a:srgbClr val="505050"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -3447,22 +3429,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="N_000002">
+        <xdr:cNvPr id="3" name="N_000002">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFF87D58-F188-A235-8D3E-4A47CA1DB42D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{902860A3-EEA7-3338-72B7-5A012F6CF547}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3477,11 +3459,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="E2EFDA"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
-        <a:ln w="25400">
+        <a:ln w="15875">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="505050"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -3531,28 +3513,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>241300</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>187325</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="31" name="C_N_000001_N_000002">
+        <xdr:cNvPr id="4" name="C_N_000001_N_000002">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBC068AE-57DC-ECE7-1151-2398747F817F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6085C1CA-BDC8-2467-105A-DAE9342BA219}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="29" idx="3"/>
-          <a:endCxn id="30" idx="1"/>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="3" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3565,9 +3547,9 @@
             <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
-        <a:ln w="25400">
+        <a:ln w="12700">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="787878"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -3591,22 +3573,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="N_000003">
+        <xdr:cNvPr id="5" name="N_000003">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A9A6ABB-706F-99DF-583F-0B209917C6CF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2A921F6-FC60-F863-41D6-FFFE74508900}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3621,11 +3603,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="E2EFDA"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
-        <a:ln w="25400">
+        <a:ln w="15875">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="505050"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -3675,28 +3657,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>241300</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="C_N_000001_N_000003">
+        <xdr:cNvPr id="6" name="C_N_000001_N_000003">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DA1C6A6-5D06-C2A6-C96C-E40A90C022CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97CF0144-FD7B-3668-4437-2A08506E47B4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="29" idx="3"/>
-          <a:endCxn id="32" idx="1"/>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="5" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3709,9 +3691,9 @@
             <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
-        <a:ln w="25400">
+        <a:ln w="12700">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="787878"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -3735,22 +3717,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="N_000004">
+        <xdr:cNvPr id="7" name="N_000004">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2656814F-2AB2-EBE5-1EC7-D60716793535}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8283E36A-2041-EB04-0D6D-D40D851CA2BB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3765,11 +3747,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
-        <a:ln w="38100">
+        <a:ln w="15875">
           <a:solidFill>
-            <a:srgbClr val="FF0000"/>
+            <a:srgbClr val="505050"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -3819,28 +3801,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>241300</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="35" name="C_N_000001_N_000004">
+        <xdr:cNvPr id="8" name="C_N_000001_N_000004">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5F07A6E-B420-DEAA-7AA6-C1022DFB3F9E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A15ADFE0-D19F-D0FE-8F44-71C77B697321}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="29" idx="3"/>
-          <a:endCxn id="34" idx="1"/>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="7" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3853,9 +3835,9 @@
             <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
-        <a:ln w="25400">
+        <a:ln w="12700">
           <a:solidFill>
-            <a:srgbClr val="FF0000"/>
+            <a:srgbClr val="787878"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -3879,22 +3861,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>111125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="N_000005">
+        <xdr:cNvPr id="9" name="N_000005">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C244732F-1553-B23B-6E57-6F087A2A3A6D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9F7AC26-C2C8-3740-E3CD-4F26AB52F164}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3909,11 +3891,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="E2EFDA"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
-        <a:ln w="25400">
+        <a:ln w="15875">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="505050"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -3963,28 +3945,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>241300</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="37" name="C_N_000001_N_000005">
+        <xdr:cNvPr id="10" name="C_N_000001_N_000005">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5BF4A82-DD3D-AB3A-9AE4-692DAE76926F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BF18F08-9518-720E-B4B8-BBD4A953D42C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="29" idx="3"/>
-          <a:endCxn id="36" idx="1"/>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="9" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3997,9 +3979,9 @@
             <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
-        <a:ln w="25400">
+        <a:ln w="12700">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="787878"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -4023,22 +4005,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
+      <xdr:colOff>463550</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>111125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="N_000006">
+        <xdr:cNvPr id="11" name="N_000006">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66B4F003-89B3-C7AD-ED49-1334BAB1BAAC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85A0472D-7BEA-BDD1-346D-0F7794C602FD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4053,7 +4035,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
         <a:ln w="15875">
           <a:solidFill>
@@ -4107,28 +4089,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
+      <xdr:colOff>463550</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="39" name="C_N_000005_N_000006">
+        <xdr:cNvPr id="12" name="C_N_000005_N_000006">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC765C90-A9E8-0F70-54AF-10902649A115}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05FD6696-FE93-292E-D1C7-04F2001CCA9E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="36" idx="3"/>
-          <a:endCxn id="38" idx="1"/>
+          <a:stCxn id="9" idx="3"/>
+          <a:endCxn id="11" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4167,22 +4149,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="N_000007">
+        <xdr:cNvPr id="13" name="N_000007">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{944900A8-06B6-CB1D-5315-74257F1B5770}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{663A32A3-A876-782D-C0B0-5274599B5A0E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4197,11 +4179,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="E2EFDA"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
-        <a:ln w="25400">
+        <a:ln w="15875">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="505050"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -4251,28 +4233,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>241300</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>111125</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="41" name="C_N_000001_N_000007">
+        <xdr:cNvPr id="14" name="C_N_000001_N_000007">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6D2C2CD-C31F-257F-4E1F-9C11D771FEAB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67FD0961-8C5A-5D84-32FF-92E7CA4D6519}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="29" idx="3"/>
-          <a:endCxn id="40" idx="1"/>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="13" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4285,9 +4267,9 @@
             <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
-        <a:ln w="25400">
+        <a:ln w="12700">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="787878"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -4311,22 +4293,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>79375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>111125</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="N_000008">
+        <xdr:cNvPr id="15" name="N_000008">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F375430-2E34-0A0F-6B2F-E2C98321F281}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09B88D5B-1A72-32B8-45B4-75E07AA13CA9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4341,11 +4323,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="E2EFDA"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
-        <a:ln w="25400">
+        <a:ln w="15875">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="505050"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -4395,28 +4377,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>241300</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="43" name="C_N_000001_N_000008">
+        <xdr:cNvPr id="16" name="C_N_000001_N_000008">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B2A858E-5523-D233-C046-05178E0EF1A7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84F55DAB-8CC6-8279-62F2-324609313DDC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="29" idx="3"/>
-          <a:endCxn id="42" idx="1"/>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="15" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4429,9 +4411,9 @@
             <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
-        <a:ln w="25400">
+        <a:ln w="12700">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="787878"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -4455,22 +4437,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="N_000009">
+        <xdr:cNvPr id="17" name="N_000009">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7F5A3FD-6FA0-47D7-4021-2BC7F4BC6B16}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAF460AD-D1C0-3E83-E870-49F26E6E736B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4485,11 +4467,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="E2EFDA"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
-        <a:ln w="25400">
+        <a:ln w="15875">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="505050"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -4539,28 +4521,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>241300</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>79375</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="45" name="C_N_000001_N_000009">
+        <xdr:cNvPr id="18" name="C_N_000001_N_000009">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2850D43F-8F09-CB56-3070-EAEEF5EC4450}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D04C1CEF-14A6-006C-D04B-087F783B7BBF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="29" idx="3"/>
-          <a:endCxn id="44" idx="1"/>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="17" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4573,9 +4555,9 @@
             <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
-        <a:ln w="25400">
+        <a:ln w="12700">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="787878"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -4599,22 +4581,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
+      <xdr:colOff>463550</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="N_000010">
+        <xdr:cNvPr id="19" name="N_000010">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A04E42B-F228-93FE-B605-2591458F4092}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71FB70C0-FA7D-DA47-8FCB-F69B33C7BFED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4629,7 +4611,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
         <a:ln w="15875">
           <a:solidFill>
@@ -4683,28 +4665,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>79375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
+      <xdr:colOff>463550</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>92075</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="47" name="C_N_000009_N_000010">
+        <xdr:cNvPr id="20" name="C_N_000009_N_000010">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2B00C30-CF70-9849-A6A4-592C8F47C81D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C411F47E-9BD2-D40B-52CB-12194962BC6E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="44" idx="3"/>
-          <a:endCxn id="46" idx="1"/>
+          <a:stCxn id="17" idx="3"/>
+          <a:endCxn id="19" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4743,22 +4725,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
+      <xdr:colOff>463550</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>79375</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="N_000011">
+        <xdr:cNvPr id="21" name="N_000011">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60A3A220-3843-59C8-9180-BED056363F38}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F089C0D-277C-186E-9A99-F98F9064C4C2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4773,7 +4755,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
         <a:ln w="15875">
           <a:solidFill>
@@ -4827,28 +4809,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>79375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
+      <xdr:colOff>463550</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="49" name="C_N_000009_N_000011">
+        <xdr:cNvPr id="22" name="C_N_000009_N_000011">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85C4A78C-7CC7-6DB2-81DE-BC43319A0A57}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5549CDC0-E967-FCD1-1357-3EC4F91AB9EB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="44" idx="3"/>
-          <a:endCxn id="48" idx="1"/>
+          <a:stCxn id="17" idx="3"/>
+          <a:endCxn id="21" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4887,22 +4869,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="N_000012">
+        <xdr:cNvPr id="23" name="N_000012">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15E477A7-4A6F-FDCC-9D8D-0260B620BE55}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EC0F93E-935A-6621-6FB4-15146247E232}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4917,11 +4899,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="E2EFDA"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
-        <a:ln w="25400">
+        <a:ln w="15875">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="505050"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -4971,28 +4953,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>241300</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="51" name="C_N_000001_N_000012">
+        <xdr:cNvPr id="24" name="C_N_000001_N_000012">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35D158D2-374D-4A87-18A6-F0B6D3805AE5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4ADD0AFE-CC55-68D9-860F-25828DDA2B2E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="29" idx="3"/>
-          <a:endCxn id="50" idx="1"/>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="23" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -5005,9 +4987,9 @@
             <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
-        <a:ln w="25400">
+        <a:ln w="12700">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="787878"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -5031,22 +5013,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
+      <xdr:colOff>463550</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="N_000013">
+        <xdr:cNvPr id="25" name="N_000013">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D05060E-3BC0-E88C-104A-E526836C747F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDBEAC2F-9CF6-4D82-6A80-60E99EB33BA5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5061,7 +5043,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
         <a:ln w="15875">
           <a:solidFill>
@@ -5115,28 +5097,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
+      <xdr:colOff>463550</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>60325</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="53" name="C_N_000012_N_000013">
+        <xdr:cNvPr id="26" name="C_N_000012_N_000013">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FCBC44C-2E42-F7D9-5967-88D9E6B4786D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C087128-22FC-0022-B9D8-0DE559F8CE9D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="50" idx="3"/>
-          <a:endCxn id="52" idx="1"/>
+          <a:stCxn id="23" idx="3"/>
+          <a:endCxn id="25" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -5175,22 +5157,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>130175</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="[1]!SelectNode" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="N_000014">
+        <xdr:cNvPr id="27" name="N_000014">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55811DDA-54E3-CF20-9749-63198BD36465}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C45FE7D-7BE7-D775-768C-FDF6F29CC406}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5205,11 +5187,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="E2EFDA"/>
+          <a:srgbClr val="C8C8C8"/>
         </a:solidFill>
-        <a:ln w="25400">
+        <a:ln w="15875">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="505050"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -5259,28 +5241,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>241300</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
+      <xdr:colOff>574675</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="55" name="C_N_000001_N_000014">
+        <xdr:cNvPr id="28" name="C_N_000001_N_000014">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D35DBAD6-C3AE-B116-70C8-5765F28DA805}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B711B4A2-2CBE-53F5-F779-55F833A849C2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="29" idx="3"/>
-          <a:endCxn id="54" idx="1"/>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="27" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -5293,9 +5275,9 @@
             <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
-        <a:ln w="25400">
+        <a:ln w="12700">
           <a:solidFill>
-            <a:srgbClr val="70AD47"/>
+            <a:srgbClr val="787878"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -5334,12 +5316,16 @@
       <definedName name="SelectNode"/>
     </definedNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5698,7 +5684,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
-        <v>735</v>
+        <v>959</v>
       </c>
       <c r="B2" s="9">
         <v>0</v>
@@ -5718,12 +5704,12 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
-        <v>736</v>
+        <v>960</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
-        <v>979</v>
+        <v>961</v>
       </c>
       <c r="B4" s="9">
         <v>1</v>
@@ -5738,7 +5724,7 @@
         <v>121</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>293</v>
@@ -5746,12 +5732,12 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
-        <v>737</v>
+        <v>962</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
-        <v>738</v>
+        <v>963</v>
       </c>
       <c r="B6" s="9">
         <v>1</v>
@@ -5774,12 +5760,12 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
-        <v>739</v>
+        <v>964</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
-        <v>740</v>
+        <v>965</v>
       </c>
       <c r="B8" s="9">
         <v>1</v>
@@ -5802,12 +5788,12 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
-        <v>741</v>
+        <v>966</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
-        <v>742</v>
+        <v>967</v>
       </c>
       <c r="B10" s="9">
         <v>1</v>
@@ -5830,12 +5816,12 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
-        <v>743</v>
+        <v>968</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
       <c r="B12" s="9">
         <v>2</v>
@@ -5850,7 +5836,7 @@
         <v>140</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>52</v>
@@ -5858,12 +5844,12 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
-        <v>744</v>
+        <v>970</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="9" t="s">
-        <v>745</v>
+        <v>971</v>
       </c>
       <c r="B14" s="9">
         <v>1</v>
@@ -5886,12 +5872,12 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
-        <v>746</v>
+        <v>972</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="9" t="s">
-        <v>747</v>
+        <v>973</v>
       </c>
       <c r="B16" s="9">
         <v>1</v>
@@ -5914,12 +5900,12 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
-        <v>748</v>
+        <v>974</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="9" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="B18" s="9">
         <v>1</v>
@@ -5934,7 +5920,7 @@
         <v>121</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>123</v>
@@ -5942,12 +5928,12 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
-        <v>749</v>
+        <v>976</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="9" t="s">
-        <v>750</v>
+        <v>977</v>
       </c>
       <c r="B20" s="9">
         <v>2</v>
@@ -5970,12 +5956,12 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
-        <v>751</v>
+        <v>978</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B22" s="9">
         <v>2</v>
@@ -5990,7 +5976,7 @@
         <v>336</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>123</v>
@@ -5998,12 +5984,12 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="10" t="s">
-        <v>752</v>
+        <v>980</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="9" t="s">
-        <v>753</v>
+        <v>981</v>
       </c>
       <c r="B24" s="9">
         <v>1</v>
@@ -6026,12 +6012,12 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
-        <v>754</v>
+        <v>982</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="9" t="s">
-        <v>755</v>
+        <v>983</v>
       </c>
       <c r="B26" s="9">
         <v>2</v>
@@ -6054,12 +6040,12 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="10" t="s">
-        <v>756</v>
+        <v>984</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="9" t="s">
-        <v>757</v>
+        <v>985</v>
       </c>
       <c r="B28" s="9">
         <v>1</v>
@@ -6082,7 +6068,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
-        <v>758</v>
+        <v>986</v>
       </c>
     </row>
   </sheetData>
@@ -6095,27 +6081,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{623CEF2B-6F90-48E7-B4F6-8425C6D15FF5}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="P33:P36"/>
+  <dimension ref="L7:Z45"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="33" spans="16:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="12:21" x14ac:dyDescent="0.4">
+      <c r="P7" t="s">
+        <v>939</v>
+      </c>
+      <c r="U7" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="10" spans="12:21" x14ac:dyDescent="0.4">
+      <c r="L10" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="33" spans="16:26" x14ac:dyDescent="0.4">
       <c r="P33" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="34" spans="16:16" x14ac:dyDescent="0.4">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="34" spans="16:26" x14ac:dyDescent="0.4">
       <c r="P34" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="35" spans="16:16" x14ac:dyDescent="0.4">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="35" spans="16:26" x14ac:dyDescent="0.4">
       <c r="P35" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="36" spans="16:16" x14ac:dyDescent="0.4">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="36" spans="16:26" x14ac:dyDescent="0.4">
       <c r="P36" t="s">
-        <v>963</v>
+        <v>939</v>
+      </c>
+    </row>
+    <row r="45" spans="16:26" x14ac:dyDescent="0.4">
+      <c r="Z45" t="s">
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -6128,7 +6132,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211E7B6E-2A29-4E12-A300-85EB807276BB}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:L135"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34.25" bestFit="1" customWidth="1"/>
@@ -6213,7 +6217,7 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I3">
         <v>177</v>
@@ -6293,7 +6297,7 @@
         <v>49</v>
       </c>
       <c r="F7" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I7">
         <v>144</v>
@@ -6313,7 +6317,7 @@
         <v>49</v>
       </c>
       <c r="F8" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I8">
         <v>147</v>
@@ -6333,7 +6337,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I9">
         <v>150</v>
@@ -6353,7 +6357,7 @@
         <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I10">
         <v>153</v>
@@ -6373,7 +6377,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I11">
         <v>156</v>
@@ -6393,7 +6397,7 @@
         <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I12">
         <v>159</v>
@@ -6453,7 +6457,7 @@
         <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I15">
         <v>362</v>
@@ -6553,7 +6557,7 @@
         <v>83</v>
       </c>
       <c r="F20" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I20">
         <v>223</v>
@@ -6573,7 +6577,7 @@
         <v>83</v>
       </c>
       <c r="F21" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I21">
         <v>229</v>
@@ -6593,7 +6597,7 @@
         <v>83</v>
       </c>
       <c r="F22" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I22">
         <v>235</v>
@@ -6633,7 +6637,7 @@
         <v>83</v>
       </c>
       <c r="F24" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I24">
         <v>302</v>
@@ -6693,7 +6697,7 @@
         <v>120</v>
       </c>
       <c r="F27" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="I27">
         <v>287</v>
@@ -6739,7 +6743,7 @@
         <v>296</v>
       </c>
       <c r="J29" t="s">
-        <v>976</v>
+        <v>946</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
@@ -6759,7 +6763,7 @@
         <v>299</v>
       </c>
       <c r="J30" t="s">
-        <v>977</v>
+        <v>947</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
@@ -6779,7 +6783,7 @@
         <v>302</v>
       </c>
       <c r="J31" t="s">
-        <v>978</v>
+        <v>948</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
@@ -6853,7 +6857,7 @@
         <v>120</v>
       </c>
       <c r="F35" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="I35">
         <v>339</v>
@@ -6913,7 +6917,7 @@
         <v>120</v>
       </c>
       <c r="F38" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="I38">
         <v>520</v>
@@ -6953,7 +6957,7 @@
         <v>120</v>
       </c>
       <c r="F40" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I40">
         <v>545</v>
@@ -7033,7 +7037,7 @@
         <v>120</v>
       </c>
       <c r="F44" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I44">
         <v>842</v>
@@ -7213,7 +7217,7 @@
         <v>120</v>
       </c>
       <c r="F53" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I53">
         <v>1623</v>
@@ -7690,10 +7694,10 @@
         <v>437</v>
       </c>
       <c r="E77" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F77" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I77">
         <v>49</v>
@@ -7710,10 +7714,10 @@
         <v>453</v>
       </c>
       <c r="E78" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F78" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I78">
         <v>52</v>
@@ -7730,10 +7734,10 @@
         <v>432</v>
       </c>
       <c r="E79" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F79" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I79">
         <v>55</v>
@@ -7750,10 +7754,10 @@
         <v>291</v>
       </c>
       <c r="E80" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F80" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I80">
         <v>93</v>
@@ -7770,10 +7774,10 @@
         <v>455</v>
       </c>
       <c r="E81" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F81" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I81">
         <v>99</v>
@@ -7790,7 +7794,7 @@
         <v>50</v>
       </c>
       <c r="E82" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F82" t="s">
         <v>49</v>
@@ -7810,7 +7814,7 @@
         <v>84</v>
       </c>
       <c r="E83" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F83" t="s">
         <v>83</v>
@@ -7830,10 +7834,10 @@
         <v>114</v>
       </c>
       <c r="E84" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F84" t="s">
-        <v>964</v>
+        <v>940</v>
       </c>
       <c r="I84">
         <v>109</v>
@@ -7853,10 +7857,10 @@
         <v>695</v>
       </c>
       <c r="E85" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F85" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I85">
         <v>185</v>
@@ -7876,10 +7880,10 @@
         <v>697</v>
       </c>
       <c r="E86" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F86" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I86">
         <v>186</v>
@@ -7899,16 +7903,16 @@
         <v>698</v>
       </c>
       <c r="E87" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F87" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I87">
         <v>187</v>
       </c>
       <c r="J87" t="s">
-        <v>957</v>
+        <v>933</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.4">
@@ -7922,10 +7926,10 @@
         <v>699</v>
       </c>
       <c r="E88" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F88" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I88">
         <v>188</v>
@@ -7945,10 +7949,10 @@
         <v>701</v>
       </c>
       <c r="E89" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F89" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I89">
         <v>192</v>
@@ -7965,7 +7969,7 @@
         <v>159</v>
       </c>
       <c r="E90" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="F90" t="s">
         <v>120</v>
@@ -7985,10 +7989,10 @@
         <v>342</v>
       </c>
       <c r="E91" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="F91" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="I91">
         <v>251</v>
@@ -8005,7 +8009,7 @@
         <v>159</v>
       </c>
       <c r="E92" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="F92" t="s">
         <v>120</v>
@@ -8025,10 +8029,10 @@
         <v>342</v>
       </c>
       <c r="E93" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="F93" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="I93">
         <v>364</v>
@@ -8045,13 +8049,13 @@
         <v>463</v>
       </c>
       <c r="E94" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F94" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I94">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="J94" t="s">
         <v>704</v>
@@ -8065,13 +8069,13 @@
         <v>474</v>
       </c>
       <c r="E95" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F95" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I95">
-        <v>94</v>
+        <v>191</v>
       </c>
       <c r="J95" t="s">
         <v>705</v>
@@ -8085,13 +8089,13 @@
         <v>463</v>
       </c>
       <c r="E96" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F96" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I96">
-        <v>162</v>
+        <v>216</v>
       </c>
       <c r="J96" t="s">
         <v>640</v>
@@ -8105,13 +8109,13 @@
         <v>441</v>
       </c>
       <c r="E97" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F97" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I97">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="J97" t="s">
         <v>706</v>
@@ -8125,13 +8129,13 @@
         <v>432</v>
       </c>
       <c r="E98" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F98" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I98">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="J98" t="s">
         <v>707</v>
@@ -8145,13 +8149,13 @@
         <v>463</v>
       </c>
       <c r="E99" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F99" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I99">
-        <v>259</v>
+        <v>313</v>
       </c>
       <c r="J99" t="s">
         <v>640</v>
@@ -8165,13 +8169,13 @@
         <v>457</v>
       </c>
       <c r="E100" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F100" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I100">
-        <v>271</v>
+        <v>325</v>
       </c>
       <c r="J100" t="s">
         <v>708</v>
@@ -8185,13 +8189,13 @@
         <v>461</v>
       </c>
       <c r="E101" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F101" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I101">
-        <v>276</v>
+        <v>330</v>
       </c>
       <c r="J101" t="s">
         <v>709</v>
@@ -8205,13 +8209,13 @@
         <v>451</v>
       </c>
       <c r="E102" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F102" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I102">
-        <v>314</v>
+        <v>372</v>
       </c>
       <c r="J102" t="s">
         <v>710</v>
@@ -8225,13 +8229,13 @@
         <v>463</v>
       </c>
       <c r="E103" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F103" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I103">
-        <v>381</v>
+        <v>439</v>
       </c>
       <c r="J103" t="s">
         <v>640</v>
@@ -8245,13 +8249,13 @@
         <v>342</v>
       </c>
       <c r="E104" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F104" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="I104">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="J104" t="s">
         <v>703</v>
@@ -8265,13 +8269,13 @@
         <v>457</v>
       </c>
       <c r="E105" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F105" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I105">
-        <v>409</v>
+        <v>467</v>
       </c>
       <c r="J105" t="s">
         <v>711</v>
@@ -8285,13 +8289,13 @@
         <v>469</v>
       </c>
       <c r="E106" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F106" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I106">
-        <v>536</v>
+        <v>594</v>
       </c>
       <c r="J106" t="s">
         <v>712</v>
@@ -8305,13 +8309,13 @@
         <v>469</v>
       </c>
       <c r="E107" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F107" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I107">
-        <v>539</v>
+        <v>597</v>
       </c>
       <c r="J107" t="s">
         <v>713</v>
@@ -8325,13 +8329,13 @@
         <v>469</v>
       </c>
       <c r="E108" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F108" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I108">
-        <v>542</v>
+        <v>600</v>
       </c>
       <c r="J108" t="s">
         <v>714</v>
@@ -8345,13 +8349,13 @@
         <v>469</v>
       </c>
       <c r="E109" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F109" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I109">
-        <v>548</v>
+        <v>606</v>
       </c>
       <c r="J109" t="s">
         <v>715</v>
@@ -8365,13 +8369,13 @@
         <v>469</v>
       </c>
       <c r="E110" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F110" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I110">
-        <v>551</v>
+        <v>609</v>
       </c>
       <c r="J110" t="s">
         <v>716</v>
@@ -8385,13 +8389,13 @@
         <v>463</v>
       </c>
       <c r="E111" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F111" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I111">
-        <v>613</v>
+        <v>671</v>
       </c>
       <c r="J111" t="s">
         <v>640</v>
@@ -8405,13 +8409,13 @@
         <v>463</v>
       </c>
       <c r="E112" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="F112" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="I112">
-        <v>682</v>
+        <v>740</v>
       </c>
       <c r="J112" t="s">
         <v>640</v>
@@ -8425,10 +8429,10 @@
         <v>539</v>
       </c>
       <c r="E113" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="F113" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="I113">
         <v>67</v>
@@ -8445,10 +8449,10 @@
         <v>546</v>
       </c>
       <c r="E114" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="F114" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="I114">
         <v>161</v>
@@ -8465,10 +8469,10 @@
         <v>313</v>
       </c>
       <c r="E115" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="F115" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I115">
         <v>261</v>
@@ -8508,7 +8512,7 @@
         <v>556</v>
       </c>
       <c r="F117" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="I117">
         <v>110</v>
@@ -8528,7 +8532,7 @@
         <v>556</v>
       </c>
       <c r="F118" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="I118">
         <v>220</v>
@@ -8548,7 +8552,7 @@
         <v>556</v>
       </c>
       <c r="F119" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="I119">
         <v>277</v>
@@ -8568,13 +8572,13 @@
         <v>556</v>
       </c>
       <c r="F120" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="I120">
         <v>298</v>
       </c>
       <c r="J120" t="s">
-        <v>958</v>
+        <v>934</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.4">
@@ -8668,7 +8672,7 @@
         <v>578</v>
       </c>
       <c r="F125" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I125">
         <v>95</v>
@@ -8688,7 +8692,7 @@
         <v>578</v>
       </c>
       <c r="F126" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I126">
         <v>100</v>
@@ -8708,7 +8712,7 @@
         <v>578</v>
       </c>
       <c r="F127" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I127">
         <v>105</v>
@@ -8728,7 +8732,7 @@
         <v>578</v>
       </c>
       <c r="F128" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I128">
         <v>110</v>
@@ -8748,7 +8752,7 @@
         <v>578</v>
       </c>
       <c r="F129" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I129">
         <v>115</v>
@@ -8768,7 +8772,7 @@
         <v>578</v>
       </c>
       <c r="F130" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="I130">
         <v>120</v>
@@ -8851,7 +8855,7 @@
         <v>120</v>
       </c>
       <c r="I134">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="J134" t="s">
         <v>275</v>
@@ -8868,18 +8872,58 @@
         <v>623</v>
       </c>
       <c r="F135" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="I135">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="J135" t="s">
         <v>392</v>
       </c>
     </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A136" t="s">
+        <v>624</v>
+      </c>
+      <c r="C136" t="s">
+        <v>949</v>
+      </c>
+      <c r="E136" t="s">
+        <v>623</v>
+      </c>
+      <c r="F136" t="s">
+        <v>944</v>
+      </c>
+      <c r="I136">
+        <v>47</v>
+      </c>
+      <c r="J136" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A137" t="s">
+        <v>624</v>
+      </c>
+      <c r="C137" t="s">
+        <v>955</v>
+      </c>
+      <c r="E137" t="s">
+        <v>623</v>
+      </c>
+      <c r="F137" t="s">
+        <v>944</v>
+      </c>
+      <c r="I137">
+        <v>51</v>
+      </c>
+      <c r="J137" t="s">
+        <v>955</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:L135">
+  <conditionalFormatting sqref="A2:L137">
     <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>$K2="○ 正常"</formula>
     </cfRule>
@@ -8894,7 +8938,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K135" xr:uid="{E5DD06D0-B7AD-4F32-83DB-EDDB3F740943}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K137" xr:uid="{E5DD06D0-B7AD-4F32-83DB-EDDB3F740943}">
       <formula1>"○ 正常,× 誤検出,△ 要確認,除外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8905,7 +8949,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3824900-6A89-4B8B-8DB9-83B3C15B4BF3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L181"/>
+  <dimension ref="A1:L183"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.125" bestFit="1" customWidth="1"/>
@@ -9112,7 +9156,7 @@
         <v>41</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>759</v>
+        <v>735</v>
       </c>
       <c r="J7" t="s">
         <v>42</v>
@@ -9150,7 +9194,7 @@
         <v>47</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>760</v>
+        <v>736</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>48</v>
@@ -9246,16 +9290,16 @@
         <v>52</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>761</v>
+        <v>737</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>762</v>
+        <v>738</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>64</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>763</v>
+        <v>739</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>65</v>
@@ -9374,16 +9418,16 @@
         <v>52</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>764</v>
+        <v>740</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>765</v>
+        <v>741</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>81</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>766</v>
+        <v>742</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>82</v>
@@ -9520,7 +9564,7 @@
         <v>84</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>767</v>
+        <v>743</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>190</v>
@@ -9584,7 +9628,7 @@
         <v>84</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>768</v>
+        <v>744</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>32</v>
@@ -9604,7 +9648,7 @@
     </row>
     <row r="22" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>964</v>
+        <v>940</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>13</v>
@@ -9692,7 +9736,7 @@
         <v>123</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>769</v>
+        <v>745</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>32</v>
@@ -9727,10 +9771,10 @@
         <v>123</v>
       </c>
       <c r="F25" t="s">
-        <v>770</v>
+        <v>746</v>
       </c>
       <c r="G25" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
       <c r="H25" t="s">
         <v>132</v>
@@ -9835,10 +9879,10 @@
         <v>123</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>772</v>
+        <v>748</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>773</v>
+        <v>749</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>149</v>
@@ -9870,7 +9914,7 @@
         <v>123</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>774</v>
+        <v>750</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>32</v>
@@ -9905,7 +9949,7 @@
         <v>123</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>775</v>
+        <v>751</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>32</v>
@@ -9943,7 +9987,7 @@
         <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>776</v>
+        <v>752</v>
       </c>
       <c r="H31" t="s">
         <v>161</v>
@@ -10080,7 +10124,7 @@
         <v>123</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>777</v>
+        <v>753</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>32</v>
@@ -10115,10 +10159,10 @@
         <v>123</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>778</v>
+        <v>754</v>
       </c>
       <c r="G36" t="s">
-        <v>779</v>
+        <v>755</v>
       </c>
       <c r="H36" t="s">
         <v>181</v>
@@ -10363,7 +10407,7 @@
         <v>123</v>
       </c>
       <c r="F43" t="s">
-        <v>780</v>
+        <v>756</v>
       </c>
       <c r="G43" t="s">
         <v>32</v>
@@ -10398,7 +10442,7 @@
         <v>123</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>780</v>
+        <v>756</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>32</v>
@@ -10433,7 +10477,7 @@
         <v>123</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>781</v>
+        <v>757</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>32</v>
@@ -10503,7 +10547,7 @@
         <v>123</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>781</v>
+        <v>757</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>32</v>
@@ -10538,7 +10582,7 @@
         <v>123</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>781</v>
+        <v>757</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>32</v>
@@ -10573,7 +10617,7 @@
         <v>123</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>781</v>
+        <v>757</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>32</v>
@@ -10608,7 +10652,7 @@
         <v>123</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>782</v>
+        <v>758</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>32</v>
@@ -10716,7 +10760,7 @@
         <v>123</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>783</v>
+        <v>759</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>32</v>
@@ -10751,7 +10795,7 @@
         <v>123</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>32</v>
@@ -10821,7 +10865,7 @@
         <v>123</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>785</v>
+        <v>761</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>32</v>
@@ -10856,7 +10900,7 @@
         <v>123</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>32</v>
@@ -10891,7 +10935,7 @@
         <v>123</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>32</v>
@@ -11016,7 +11060,7 @@
     </row>
     <row r="62" spans="1:12" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.4">
       <c r="A62" s="5" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>36</v>
@@ -11025,7 +11069,7 @@
         <v>287</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>786</v>
+        <v>762</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>52</v>
@@ -11034,10 +11078,10 @@
         <v>626</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>787</v>
+        <v>763</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>788</v>
+        <v>764</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>288</v>
@@ -11051,7 +11095,7 @@
     </row>
     <row r="63" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A63" s="5" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>13</v>
@@ -11060,16 +11104,16 @@
         <v>289</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>789</v>
+        <v>765</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>52</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>790</v>
+        <v>766</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>791</v>
+        <v>767</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>290</v>
@@ -11083,7 +11127,7 @@
     </row>
     <row r="64" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A64" s="5" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>36</v>
@@ -11121,7 +11165,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -11159,7 +11203,7 @@
     </row>
     <row r="66" spans="1:12" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="B66" t="s">
         <v>36</v>
@@ -11174,10 +11218,10 @@
         <v>52</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>792</v>
+        <v>768</v>
       </c>
       <c r="G66" t="s">
-        <v>793</v>
+        <v>769</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>308</v>
@@ -11194,7 +11238,7 @@
     </row>
     <row r="67" spans="1:12" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="B67" t="s">
         <v>36</v>
@@ -11209,10 +11253,10 @@
         <v>52</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>794</v>
+        <v>770</v>
       </c>
       <c r="G67" t="s">
-        <v>793</v>
+        <v>769</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>311</v>
@@ -11229,7 +11273,7 @@
     </row>
     <row r="68" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="B68" t="s">
         <v>36</v>
@@ -11267,7 +11311,7 @@
     </row>
     <row r="69" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A69" s="5" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>36</v>
@@ -11282,7 +11326,7 @@
         <v>52</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>795</v>
+        <v>771</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>315</v>
@@ -11302,7 +11346,7 @@
     </row>
     <row r="70" spans="1:12" ht="75" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="B70" t="s">
         <v>36</v>
@@ -11340,7 +11384,7 @@
     </row>
     <row r="71" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A71" s="3" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>13</v>
@@ -11378,7 +11422,7 @@
     </row>
     <row r="72" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A72" s="5" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>13</v>
@@ -11416,7 +11460,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="B73" t="s">
         <v>36</v>
@@ -11454,7 +11498,7 @@
     </row>
     <row r="74" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A74" s="5" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>36</v>
@@ -11498,7 +11542,7 @@
         <v>353</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>796</v>
+        <v>772</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>123</v>
@@ -11510,10 +11554,10 @@
         <v>32</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>797</v>
+        <v>773</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>798</v>
+        <v>774</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>354</v>
@@ -11536,7 +11580,7 @@
         <v>362</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>799</v>
+        <v>775</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>123</v>
@@ -11548,10 +11592,10 @@
         <v>32</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>800</v>
+        <v>776</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>801</v>
+        <v>777</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>363</v>
@@ -11574,28 +11618,28 @@
         <v>355</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>802</v>
+        <v>778</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>123</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>803</v>
+        <v>779</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>804</v>
+        <v>780</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>805</v>
+        <v>781</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>356</v>
       </c>
       <c r="K77" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>16</v>
@@ -11612,7 +11656,7 @@
         <v>364</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>806</v>
+        <v>782</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>123</v>
@@ -11624,10 +11668,10 @@
         <v>32</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>807</v>
+        <v>783</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>365</v>
@@ -11650,7 +11694,7 @@
         <v>366</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>809</v>
+        <v>785</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>123</v>
@@ -11662,7 +11706,7 @@
         <v>32</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>810</v>
+        <v>786</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>367</v>
@@ -11685,7 +11729,7 @@
         <v>368</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>811</v>
+        <v>787</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>123</v>
@@ -11697,7 +11741,7 @@
         <v>32</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>812</v>
+        <v>788</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>369</v>
@@ -11720,7 +11764,7 @@
         <v>370</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>813</v>
+        <v>789</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>123</v>
@@ -11732,10 +11776,10 @@
         <v>32</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>814</v>
+        <v>790</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>815</v>
+        <v>791</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>371</v>
@@ -11758,7 +11802,7 @@
         <v>372</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>816</v>
+        <v>792</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>123</v>
@@ -11770,10 +11814,10 @@
         <v>32</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>817</v>
+        <v>793</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>818</v>
+        <v>794</v>
       </c>
       <c r="J82" s="3" t="s">
         <v>373</v>
@@ -11796,22 +11840,22 @@
         <v>374</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>819</v>
+        <v>795</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>783</v>
+        <v>759</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>820</v>
+        <v>796</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>821</v>
+        <v>797</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>375</v>
@@ -11834,7 +11878,7 @@
         <v>353</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>822</v>
+        <v>798</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>123</v>
@@ -11846,10 +11890,10 @@
         <v>32</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>823</v>
+        <v>799</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>824</v>
+        <v>800</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>354</v>
@@ -11872,7 +11916,7 @@
         <v>377</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>825</v>
+        <v>801</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>123</v>
@@ -11884,7 +11928,7 @@
         <v>32</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>826</v>
+        <v>802</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>378</v>
@@ -11907,7 +11951,7 @@
         <v>379</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>827</v>
+        <v>803</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>123</v>
@@ -11919,10 +11963,10 @@
         <v>32</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>828</v>
+        <v>804</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>829</v>
+        <v>805</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>380</v>
@@ -11945,7 +11989,7 @@
         <v>381</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>830</v>
+        <v>806</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>123</v>
@@ -11957,7 +12001,7 @@
         <v>32</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>831</v>
+        <v>807</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>382</v>
@@ -11980,7 +12024,7 @@
         <v>383</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>832</v>
+        <v>808</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>123</v>
@@ -11992,7 +12036,7 @@
         <v>32</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>833</v>
+        <v>809</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>384</v>
@@ -12015,7 +12059,7 @@
         <v>385</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>834</v>
+        <v>810</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>123</v>
@@ -12027,7 +12071,7 @@
         <v>32</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>835</v>
+        <v>811</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>386</v>
@@ -12041,7 +12085,7 @@
     </row>
     <row r="90" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A90" s="5" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>13</v>
@@ -12079,7 +12123,7 @@
     </row>
     <row r="91" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -12117,7 +12161,7 @@
     </row>
     <row r="92" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A92" s="3" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>13</v>
@@ -12138,7 +12182,7 @@
         <v>32</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>836</v>
+        <v>812</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>400</v>
@@ -12152,7 +12196,7 @@
     </row>
     <row r="93" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A93" s="5" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>36</v>
@@ -12190,7 +12234,7 @@
     </row>
     <row r="94" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>13</v>
@@ -12225,7 +12269,7 @@
     </row>
     <row r="95" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A95" s="5" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>36</v>
@@ -12269,7 +12313,7 @@
         <v>353</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>837</v>
+        <v>813</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>25</v>
@@ -12281,7 +12325,7 @@
         <v>32</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>838</v>
+        <v>814</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>354</v>
@@ -12304,7 +12348,7 @@
         <v>416</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>839</v>
+        <v>815</v>
       </c>
       <c r="E97" s="5" t="s">
         <v>25</v>
@@ -12316,7 +12360,7 @@
         <v>32</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>840</v>
+        <v>816</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>417</v>
@@ -12339,7 +12383,7 @@
         <v>418</v>
       </c>
       <c r="D98" t="s">
-        <v>841</v>
+        <v>817</v>
       </c>
       <c r="E98" t="s">
         <v>25</v>
@@ -12351,10 +12395,10 @@
         <v>32</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>842</v>
+        <v>818</v>
       </c>
       <c r="I98" t="s">
-        <v>843</v>
+        <v>819</v>
       </c>
       <c r="J98" t="s">
         <v>419</v>
@@ -12377,7 +12421,7 @@
         <v>420</v>
       </c>
       <c r="D99" t="s">
-        <v>844</v>
+        <v>820</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
@@ -12389,7 +12433,7 @@
         <v>32</v>
       </c>
       <c r="H99" t="s">
-        <v>845</v>
+        <v>821</v>
       </c>
       <c r="J99" t="s">
         <v>421</v>
@@ -12412,13 +12456,13 @@
         <v>359</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>846</v>
+        <v>822</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>847</v>
+        <v>823</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>360</v>
@@ -12441,13 +12485,13 @@
         <v>422</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>848</v>
+        <v>824</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>849</v>
+        <v>825</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>423</v>
@@ -12470,13 +12514,13 @@
         <v>424</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>850</v>
+        <v>826</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>851</v>
+        <v>827</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>425</v>
@@ -12499,19 +12543,19 @@
         <v>426</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>852</v>
+        <v>828</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>853</v>
+        <v>829</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>854</v>
+        <v>830</v>
       </c>
       <c r="J103" s="3" t="s">
         <v>427</v>
@@ -12534,7 +12578,7 @@
         <v>428</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>855</v>
+        <v>831</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>25</v>
@@ -12546,10 +12590,10 @@
         <v>32</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>856</v>
+        <v>832</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>857</v>
+        <v>833</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>429</v>
@@ -12572,13 +12616,13 @@
         <v>430</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>858</v>
+        <v>834</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>859</v>
+        <v>835</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>431</v>
@@ -12590,68 +12634,47 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
-        <v>968</v>
-      </c>
-      <c r="B106" t="s">
-        <v>36</v>
-      </c>
-      <c r="C106" t="s">
-        <v>432</v>
-      </c>
-      <c r="D106" t="s">
-        <v>433</v>
-      </c>
-      <c r="E106" t="s">
-        <v>434</v>
-      </c>
-      <c r="F106" t="s">
-        <v>32</v>
-      </c>
-      <c r="G106" t="s">
-        <v>860</v>
-      </c>
-      <c r="H106" t="s">
-        <v>435</v>
-      </c>
-      <c r="J106" t="s">
-        <v>436</v>
-      </c>
-      <c r="K106">
-        <v>3</v>
-      </c>
-      <c r="L106" t="s">
-        <v>43</v>
+    <row r="106" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A106" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>949</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>950</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="K106" s="5">
+        <v>1</v>
+      </c>
+      <c r="L106" s="5" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="107" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A107" s="5" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="H107" s="5" t="s">
-        <v>439</v>
+        <v>953</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>440</v>
+        <v>954</v>
       </c>
       <c r="K107" s="5">
         <v>1</v>
@@ -12660,161 +12683,128 @@
         <v>57</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="75" x14ac:dyDescent="0.4">
-      <c r="A108" t="s">
-        <v>968</v>
-      </c>
-      <c r="B108" t="s">
+    <row r="108" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A108" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="B108" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C108" t="s">
-        <v>969</v>
-      </c>
-      <c r="D108" t="s">
-        <v>970</v>
-      </c>
-      <c r="E108" t="s">
-        <v>609</v>
-      </c>
-      <c r="F108" t="s">
-        <v>32</v>
-      </c>
-      <c r="G108" t="s">
-        <v>32</v>
-      </c>
-      <c r="H108" t="s">
-        <v>971</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>972</v>
-      </c>
-      <c r="J108" t="s">
-        <v>973</v>
-      </c>
-      <c r="K108">
-        <v>2</v>
-      </c>
-      <c r="L108" t="s">
+      <c r="C108" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="J108" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="K108" s="5">
+        <v>1</v>
+      </c>
+      <c r="L108" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A109" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="K109" s="3">
+        <v>0</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>944</v>
+      </c>
+      <c r="B110" t="s">
+        <v>36</v>
+      </c>
+      <c r="C110" t="s">
+        <v>432</v>
+      </c>
+      <c r="D110" t="s">
+        <v>433</v>
+      </c>
+      <c r="E110" t="s">
+        <v>434</v>
+      </c>
+      <c r="F110" t="s">
+        <v>32</v>
+      </c>
+      <c r="G110" t="s">
+        <v>836</v>
+      </c>
+      <c r="H110" t="s">
+        <v>435</v>
+      </c>
+      <c r="J110" t="s">
+        <v>436</v>
+      </c>
+      <c r="K110">
+        <v>3</v>
+      </c>
+      <c r="L110" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="109" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="5" t="s">
-        <v>968</v>
-      </c>
-      <c r="B109" s="5" t="s">
+    <row r="111" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="E109" s="5" t="s">
+      <c r="C111" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E111" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="F109" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>861</v>
-      </c>
-      <c r="H109" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="J109" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="K109" s="5">
+      <c r="F111" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="K111" s="5">
         <v>1</v>
       </c>
-      <c r="L109" s="5" t="s">
+      <c r="L111" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="110" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="3" t="s">
-        <v>968</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>861</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="K110" s="3">
-        <v>0</v>
-      </c>
-      <c r="L110" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A111" s="3" t="s">
-        <v>968</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>862</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>863</v>
-      </c>
-      <c r="J111" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="K111" s="3">
-        <v>0</v>
-      </c>
-      <c r="L111" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A112" s="5" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>864</v>
+        <v>442</v>
       </c>
       <c r="E112" s="5" t="s">
         <v>434</v>
@@ -12823,16 +12813,13 @@
         <v>39</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>476</v>
+        <v>837</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>865</v>
-      </c>
-      <c r="I112" s="6" t="s">
-        <v>866</v>
+        <v>443</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="K112" s="5">
         <v>1</v>
@@ -12841,91 +12828,88 @@
         <v>57</v>
       </c>
     </row>
-    <row r="113" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="5" t="s">
-        <v>968</v>
-      </c>
-      <c r="B113" s="5" t="s">
+    <row r="113" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="B113" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C113" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>867</v>
-      </c>
-      <c r="E113" s="5" t="s">
+      <c r="C113" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="E113" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="F113" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="H113" s="5" t="s">
-        <v>868</v>
-      </c>
-      <c r="J113" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="K113" s="5">
-        <v>1</v>
-      </c>
-      <c r="L113" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A114" s="5" t="s">
-        <v>968</v>
-      </c>
-      <c r="B114" s="5" t="s">
+      <c r="F113" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="K113" s="3">
+        <v>0</v>
+      </c>
+      <c r="L113" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A114" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C114" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>869</v>
-      </c>
-      <c r="E114" s="5" t="s">
+      <c r="C114" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="E114" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="F114" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="H114" s="5" t="s">
-        <v>871</v>
-      </c>
-      <c r="I114" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="J114" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="K114" s="5">
-        <v>1</v>
-      </c>
-      <c r="L114" s="5" t="s">
-        <v>57</v>
+      <c r="F114" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="K114" s="3">
+        <v>0</v>
+      </c>
+      <c r="L114" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="B115" t="s">
         <v>36</v>
       </c>
       <c r="C115" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D115" t="s">
-        <v>872</v>
+        <v>840</v>
       </c>
       <c r="E115" t="s">
         <v>434</v>
@@ -12934,86 +12918,89 @@
         <v>39</v>
       </c>
       <c r="G115" t="s">
-        <v>873</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>874</v>
+        <v>476</v>
+      </c>
+      <c r="H115" t="s">
+        <v>841</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>842</v>
       </c>
       <c r="J115" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="K115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L115" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="116" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A116" s="3" t="s">
-        <v>968</v>
-      </c>
-      <c r="B116" s="3" t="s">
+    <row r="116" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C116" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="E116" s="3" t="s">
+      <c r="C116" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="E116" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="F116" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>873</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>876</v>
-      </c>
-      <c r="J116" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="K116" s="3">
-        <v>0</v>
-      </c>
-      <c r="L116" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" s="5" customFormat="1" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="F116" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="H116" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="J116" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="K116" s="5">
+        <v>1</v>
+      </c>
+      <c r="L116" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A117" s="5" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>877</v>
+        <v>845</v>
       </c>
       <c r="E117" s="5" t="s">
         <v>434</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>878</v>
+        <v>846</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>476</v>
+        <v>542</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>879</v>
-      </c>
-      <c r="I117" s="6" t="s">
-        <v>880</v>
+        <v>847</v>
+      </c>
+      <c r="I117" s="5" t="s">
+        <v>297</v>
       </c>
       <c r="J117" s="5" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="K117" s="5">
         <v>1</v>
@@ -13024,16 +13011,16 @@
     </row>
     <row r="118" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="B118" t="s">
         <v>36</v>
       </c>
       <c r="C118" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D118" t="s">
-        <v>464</v>
+        <v>848</v>
       </c>
       <c r="E118" t="s">
         <v>434</v>
@@ -13042,282 +13029,276 @@
         <v>39</v>
       </c>
       <c r="G118" t="s">
-        <v>465</v>
+        <v>849</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="I118" t="s">
-        <v>467</v>
+        <v>850</v>
       </c>
       <c r="J118" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="K118">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L118" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A119" t="s">
-        <v>968</v>
-      </c>
-      <c r="B119" t="s">
+    <row r="119" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A119" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K119" s="3">
+        <v>0</v>
+      </c>
+      <c r="L119" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" s="5" customFormat="1" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A120" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="H120" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="I120" s="6" t="s">
+        <v>856</v>
+      </c>
+      <c r="J120" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="K120" s="5">
+        <v>1</v>
+      </c>
+      <c r="L120" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>944</v>
+      </c>
+      <c r="B121" t="s">
+        <v>36</v>
+      </c>
+      <c r="C121" t="s">
+        <v>463</v>
+      </c>
+      <c r="D121" t="s">
+        <v>464</v>
+      </c>
+      <c r="E121" t="s">
+        <v>434</v>
+      </c>
+      <c r="F121" t="s">
+        <v>39</v>
+      </c>
+      <c r="G121" t="s">
+        <v>465</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="I121" t="s">
+        <v>467</v>
+      </c>
+      <c r="J121" t="s">
+        <v>468</v>
+      </c>
+      <c r="K121">
+        <v>7</v>
+      </c>
+      <c r="L121" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>944</v>
+      </c>
+      <c r="B122" t="s">
+        <v>36</v>
+      </c>
+      <c r="C122" t="s">
         <v>469</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D122" t="s">
         <v>470</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E122" t="s">
         <v>434</v>
       </c>
-      <c r="F119" t="s">
+      <c r="F122" t="s">
         <v>471</v>
       </c>
-      <c r="G119" t="s">
-        <v>881</v>
-      </c>
-      <c r="H119" t="s">
+      <c r="G122" t="s">
+        <v>857</v>
+      </c>
+      <c r="H122" t="s">
         <v>472</v>
       </c>
-      <c r="J119" t="s">
+      <c r="J122" t="s">
         <v>473</v>
       </c>
-      <c r="K119">
+      <c r="K122">
         <v>5</v>
       </c>
-      <c r="L119" t="s">
+      <c r="L122" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A120" t="s">
-        <v>968</v>
-      </c>
-      <c r="B120" t="s">
+    <row r="123" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>944</v>
+      </c>
+      <c r="B123" t="s">
         <v>36</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C123" t="s">
         <v>474</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D123" t="s">
         <v>475</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E123" t="s">
         <v>434</v>
       </c>
-      <c r="F120" t="s">
+      <c r="F123" t="s">
         <v>39</v>
       </c>
-      <c r="G120" t="s">
+      <c r="G123" t="s">
         <v>476</v>
       </c>
-      <c r="H120" s="1" t="s">
+      <c r="H123" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="I120" t="s">
+      <c r="I123" t="s">
         <v>478</v>
       </c>
-      <c r="J120" t="s">
+      <c r="J123" t="s">
         <v>479</v>
       </c>
-      <c r="K120">
+      <c r="K123">
         <v>2</v>
       </c>
-      <c r="L120" t="s">
+      <c r="L123" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="121" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A121" s="3" t="s">
-        <v>968</v>
-      </c>
-      <c r="B121" s="3" t="s">
+    <row r="124" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A124" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="B124" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C124" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="D124" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="E121" s="3" t="s">
+      <c r="E124" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="F121" s="3" t="s">
+      <c r="F124" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="G121" s="3" t="s">
+      <c r="G124" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="H121" s="4" t="s">
+      <c r="H124" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="I121" s="3" t="s">
+      <c r="I124" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="J121" s="3" t="s">
+      <c r="J124" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="K121" s="3">
+      <c r="K124" s="3">
         <v>0</v>
       </c>
-      <c r="L121" s="3" t="s">
+      <c r="L124" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A122" s="3" t="s">
-        <v>968</v>
-      </c>
-      <c r="B122" s="3" t="s">
+    <row r="125" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A125" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C125" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="D122" s="3" t="s">
+      <c r="D125" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="E122" s="3" t="s">
+      <c r="E125" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="F122" s="3" t="s">
+      <c r="F125" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G122" s="3" t="s">
+      <c r="G125" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="H122" s="4" t="s">
+      <c r="H125" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="J122" s="3" t="s">
+      <c r="J125" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="K122" s="3">
+      <c r="K125" s="3">
         <v>0</v>
       </c>
-      <c r="L122" s="3" t="s">
+      <c r="L125" s="3" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="J123" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="K123" s="2">
-        <v>6</v>
-      </c>
-      <c r="L123" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" s="2" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A124" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>885</v>
-      </c>
-      <c r="I124" s="11" t="s">
-        <v>886</v>
-      </c>
-      <c r="J124" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="K124" s="2">
-        <v>0</v>
-      </c>
-      <c r="L124" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" s="2" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A125" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F125" s="11" t="s">
-        <v>803</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="I125" s="11" t="s">
-        <v>889</v>
-      </c>
-      <c r="J125" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K125" s="2">
-        <v>2</v>
-      </c>
-      <c r="L125" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="126" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
@@ -13328,10 +13309,10 @@
         <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>491</v>
+        <v>353</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>168</v>
+        <v>858</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>123</v>
@@ -13343,22 +13324,22 @@
         <v>32</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>890</v>
+        <v>859</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>891</v>
+        <v>860</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>492</v>
+        <v>354</v>
       </c>
       <c r="K126" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L126" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="127" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:12" s="2" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A127" s="2" t="s">
         <v>490</v>
       </c>
@@ -13366,10 +13347,10 @@
         <v>13</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>493</v>
+        <v>357</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>172</v>
+        <v>789</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>123</v>
@@ -13381,10 +13362,13 @@
         <v>32</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>892</v>
+        <v>861</v>
+      </c>
+      <c r="I127" s="11" t="s">
+        <v>862</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>494</v>
+        <v>358</v>
       </c>
       <c r="K127" s="2">
         <v>0</v>
@@ -13393,7 +13377,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:12" s="2" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A128" s="2" t="s">
         <v>490</v>
       </c>
@@ -13401,28 +13385,31 @@
         <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>495</v>
+        <v>355</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>199</v>
+        <v>863</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F128" s="2" t="s">
-        <v>32</v>
+      <c r="F128" s="11" t="s">
+        <v>779</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>893</v>
+        <v>864</v>
+      </c>
+      <c r="I128" s="11" t="s">
+        <v>865</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>496</v>
+        <v>356</v>
       </c>
       <c r="K128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="2" t="s">
         <v>16</v>
@@ -13436,10 +13423,10 @@
         <v>13</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>123</v>
@@ -13451,10 +13438,13 @@
         <v>32</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>894</v>
+        <v>866</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>867</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="K129" s="2">
         <v>0</v>
@@ -13471,10 +13461,10 @@
         <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>123</v>
@@ -13486,10 +13476,10 @@
         <v>32</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>895</v>
+        <v>868</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="K130" s="2">
         <v>0</v>
@@ -13506,10 +13496,10 @@
         <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>366</v>
+        <v>495</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>243</v>
+        <v>199</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>123</v>
@@ -13521,51 +13511,51 @@
         <v>32</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>896</v>
+        <v>869</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>367</v>
+        <v>496</v>
       </c>
       <c r="K131" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="5" t="s">
+    <row r="132" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B132" s="5" t="s">
+      <c r="B132" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C132" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>897</v>
-      </c>
-      <c r="E132" s="5" t="s">
+      <c r="C132" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F132" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G132" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H132" s="5" t="s">
-        <v>898</v>
-      </c>
-      <c r="J132" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="K132" s="5">
-        <v>1</v>
-      </c>
-      <c r="L132" s="5" t="s">
-        <v>57</v>
+      <c r="F132" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="K132" s="2">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="133" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
@@ -13576,10 +13566,10 @@
         <v>13</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>899</v>
+        <v>207</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>123</v>
@@ -13591,10 +13581,10 @@
         <v>32</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>900</v>
+        <v>871</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="K133" s="2">
         <v>0</v>
@@ -13603,115 +13593,112 @@
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A134" s="3" t="s">
+    <row r="134" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C134" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>901</v>
-      </c>
-      <c r="E134" s="3" t="s">
+      <c r="C134" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F134" s="4" t="s">
-        <v>902</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="I134" s="3" t="s">
-        <v>903</v>
-      </c>
-      <c r="J134" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="K134" s="3">
+      <c r="F134" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="K134" s="2">
+        <v>1</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H135" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="J135" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="K135" s="5">
+        <v>1</v>
+      </c>
+      <c r="L135" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="K136" s="2">
         <v>0</v>
       </c>
-      <c r="L134" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.4">
-      <c r="A135" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>901</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>904</v>
-      </c>
-      <c r="G135" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H135" s="3" t="s">
-        <v>905</v>
-      </c>
-      <c r="J135" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="K135" s="3">
-        <v>0</v>
-      </c>
-      <c r="L135" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.4">
-      <c r="A136" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="D136" s="3" t="s">
-        <v>901</v>
-      </c>
-      <c r="E136" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F136" s="4" t="s">
-        <v>904</v>
-      </c>
-      <c r="G136" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H136" s="3" t="s">
-        <v>905</v>
-      </c>
-      <c r="J136" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="K136" s="3">
-        <v>0</v>
-      </c>
-      <c r="L136" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.4">
+      <c r="L136" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A137" s="3" t="s">
         <v>490</v>
       </c>
@@ -13719,25 +13706,28 @@
         <v>13</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>901</v>
+        <v>877</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>904</v>
+        <v>878</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>905</v>
+        <v>303</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>879</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="K137" s="3">
         <v>0</v>
@@ -13754,25 +13744,25 @@
         <v>13</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>901</v>
+        <v>877</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>904</v>
+        <v>880</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>905</v>
+        <v>881</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="K138" s="3">
         <v>0</v>
@@ -13789,25 +13779,25 @@
         <v>13</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>901</v>
+        <v>877</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>904</v>
+        <v>880</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>905</v>
+        <v>881</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="K139" s="3">
         <v>0</v>
@@ -13824,25 +13814,25 @@
         <v>13</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>901</v>
+        <v>877</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>904</v>
+        <v>880</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>905</v>
+        <v>881</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="K140" s="3">
         <v>0</v>
@@ -13851,33 +13841,33 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.4">
       <c r="A141" s="3" t="s">
-        <v>316</v>
+        <v>490</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>906</v>
+        <v>877</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>907</v>
-      </c>
-      <c r="F141" s="3" t="s">
-        <v>32</v>
+        <v>123</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>880</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>908</v>
+        <v>881</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="K141" s="3">
         <v>0</v>
@@ -13886,36 +13876,33 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.4">
       <c r="A142" s="3" t="s">
-        <v>316</v>
+        <v>490</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>909</v>
+        <v>877</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>907</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>315</v>
+        <v>123</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>880</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>910</v>
-      </c>
-      <c r="I142" s="3" t="s">
-        <v>911</v>
+        <v>881</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="K142" s="3">
         <v>0</v>
@@ -13924,36 +13911,33 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.4">
       <c r="A143" s="3" t="s">
-        <v>316</v>
+        <v>490</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>912</v>
+        <v>877</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>907</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>315</v>
+        <v>123</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>880</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>913</v>
-      </c>
-      <c r="I143" s="3" t="s">
-        <v>911</v>
+        <v>881</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="K143" s="3">
         <v>0</v>
@@ -13967,28 +13951,28 @@
         <v>316</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>914</v>
+        <v>882</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>907</v>
+        <v>883</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>32</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>915</v>
+        <v>32</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>916</v>
+        <v>884</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="K144" s="3">
         <v>0</v>
@@ -14002,28 +13986,31 @@
         <v>316</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>917</v>
+        <v>885</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>907</v>
+        <v>883</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>32</v>
+        <v>315</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>918</v>
+        <v>32</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>919</v>
+        <v>886</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>887</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="K145" s="3">
         <v>0</v>
@@ -14032,179 +14019,176 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A146" t="s">
+    <row r="146" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A146" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="K146" s="3">
+        <v>0</v>
+      </c>
+      <c r="L146" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A147" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B147" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C147" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="K147" s="3">
+        <v>0</v>
+      </c>
+      <c r="L147" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A148" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="J148" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="K148" s="3">
+        <v>0</v>
+      </c>
+      <c r="L148" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A149" t="s">
+        <v>316</v>
+      </c>
+      <c r="B149" t="s">
+        <v>36</v>
+      </c>
+      <c r="C149" t="s">
         <v>529</v>
       </c>
-      <c r="D146" t="s">
-        <v>920</v>
-      </c>
-      <c r="E146" t="s">
-        <v>921</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="G146" t="s">
-        <v>923</v>
-      </c>
-      <c r="H146" s="1" t="s">
-        <v>924</v>
-      </c>
-      <c r="J146" t="s">
+      <c r="D149" t="s">
+        <v>896</v>
+      </c>
+      <c r="E149" t="s">
+        <v>897</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="G149" t="s">
+        <v>899</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="J149" t="s">
         <v>530</v>
       </c>
-      <c r="K146">
+      <c r="K149">
         <v>2</v>
       </c>
-      <c r="L146" t="s">
+      <c r="L149" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A147" t="s">
+    <row r="150" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A150" t="s">
         <v>316</v>
-      </c>
-      <c r="B147" t="s">
-        <v>36</v>
-      </c>
-      <c r="C147" t="s">
-        <v>531</v>
-      </c>
-      <c r="D147" t="s">
-        <v>925</v>
-      </c>
-      <c r="E147" t="s">
-        <v>921</v>
-      </c>
-      <c r="F147" t="s">
-        <v>926</v>
-      </c>
-      <c r="G147" t="s">
-        <v>302</v>
-      </c>
-      <c r="H147" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="J147" t="s">
-        <v>532</v>
-      </c>
-      <c r="K147">
-        <v>2</v>
-      </c>
-      <c r="L147" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A148" t="s">
-        <v>974</v>
-      </c>
-      <c r="B148" t="s">
-        <v>36</v>
-      </c>
-      <c r="C148" t="s">
-        <v>533</v>
-      </c>
-      <c r="D148" t="s">
-        <v>534</v>
-      </c>
-      <c r="E148" t="s">
-        <v>123</v>
-      </c>
-      <c r="F148" t="s">
-        <v>535</v>
-      </c>
-      <c r="G148" t="s">
-        <v>928</v>
-      </c>
-      <c r="H148" t="s">
-        <v>536</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="J148" t="s">
-        <v>538</v>
-      </c>
-      <c r="K148">
-        <v>2</v>
-      </c>
-      <c r="L148" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.4">
-      <c r="A149" s="5" t="s">
-        <v>974</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>541</v>
-      </c>
-      <c r="G149" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="H149" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="I149" s="6" t="s">
-        <v>544</v>
-      </c>
-      <c r="J149" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="K149" s="5">
-        <v>1</v>
-      </c>
-      <c r="L149" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A150" t="s">
-        <v>974</v>
       </c>
       <c r="B150" t="s">
         <v>36</v>
       </c>
       <c r="C150" t="s">
-        <v>546</v>
+        <v>531</v>
       </c>
       <c r="D150" t="s">
-        <v>547</v>
+        <v>901</v>
       </c>
       <c r="E150" t="s">
-        <v>123</v>
+        <v>897</v>
       </c>
       <c r="F150" t="s">
-        <v>315</v>
+        <v>902</v>
       </c>
       <c r="G150" t="s">
-        <v>929</v>
-      </c>
-      <c r="H150" t="s">
-        <v>548</v>
+        <v>302</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>903</v>
       </c>
       <c r="J150" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="K150">
         <v>2</v>
@@ -14213,36 +14197,36 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="75" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="B151" t="s">
         <v>36</v>
       </c>
       <c r="C151" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="D151" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="E151" t="s">
         <v>123</v>
       </c>
-      <c r="F151" s="1" t="s">
-        <v>552</v>
+      <c r="F151" t="s">
+        <v>535</v>
       </c>
       <c r="G151" t="s">
-        <v>930</v>
-      </c>
-      <c r="H151" s="1" t="s">
-        <v>553</v>
+        <v>904</v>
+      </c>
+      <c r="H151" t="s">
+        <v>536</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="J151" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="K151">
         <v>2</v>
@@ -14251,36 +14235,36 @@
         <v>43</v>
       </c>
     </row>
-    <row r="152" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:12" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.4">
       <c r="A152" s="5" t="s">
-        <v>556</v>
+        <v>945</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="E152" s="5" t="s">
         <v>123</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>331</v>
+        <v>541</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>560</v>
+        <v>542</v>
+      </c>
+      <c r="H152" s="5" t="s">
+        <v>543</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="J152" s="5" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="K152" s="5">
         <v>1</v>
@@ -14289,77 +14273,77 @@
         <v>57</v>
       </c>
     </row>
-    <row r="153" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A153" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="E153" s="3" t="s">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A153" t="s">
+        <v>945</v>
+      </c>
+      <c r="B153" t="s">
+        <v>36</v>
+      </c>
+      <c r="C153" t="s">
+        <v>546</v>
+      </c>
+      <c r="D153" t="s">
+        <v>547</v>
+      </c>
+      <c r="E153" t="s">
         <v>123</v>
       </c>
-      <c r="F153" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="G153" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H153" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="J153" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="K153" s="3">
-        <v>0</v>
-      </c>
-      <c r="L153" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.4">
-      <c r="A154" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="D154" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="E154" s="3" t="s">
+      <c r="F153" t="s">
+        <v>315</v>
+      </c>
+      <c r="G153" t="s">
+        <v>905</v>
+      </c>
+      <c r="H153" t="s">
+        <v>548</v>
+      </c>
+      <c r="J153" t="s">
+        <v>549</v>
+      </c>
+      <c r="K153">
+        <v>2</v>
+      </c>
+      <c r="L153" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" ht="75" x14ac:dyDescent="0.4">
+      <c r="A154" t="s">
+        <v>945</v>
+      </c>
+      <c r="B154" t="s">
+        <v>36</v>
+      </c>
+      <c r="C154" t="s">
+        <v>550</v>
+      </c>
+      <c r="D154" t="s">
+        <v>551</v>
+      </c>
+      <c r="E154" t="s">
         <v>123</v>
       </c>
-      <c r="F154" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H154" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="I154" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="J154" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="K154" s="3">
-        <v>0</v>
-      </c>
-      <c r="L154" s="3" t="s">
-        <v>28</v>
+      <c r="F154" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="G154" t="s">
+        <v>906</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="J154" t="s">
+        <v>555</v>
+      </c>
+      <c r="K154">
+        <v>2</v>
+      </c>
+      <c r="L154" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="155" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
@@ -14370,28 +14354,28 @@
         <v>13</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="E155" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F155" s="5" t="s">
-        <v>32</v>
+      <c r="F155" s="6" t="s">
+        <v>331</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>931</v>
-      </c>
-      <c r="H155" s="5" t="s">
-        <v>575</v>
+        <v>559</v>
+      </c>
+      <c r="H155" s="6" t="s">
+        <v>560</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="J155" s="5" t="s">
-        <v>577</v>
+        <v>562</v>
       </c>
       <c r="K155" s="5">
         <v>1</v>
@@ -14400,18 +14384,33 @@
         <v>57</v>
       </c>
     </row>
-    <row r="156" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A156" s="3" t="s">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>579</v>
+        <v>563</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>565</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="K156" s="3">
         <v>0</v>
@@ -14420,36 +14419,36 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.4">
       <c r="A157" s="3" t="s">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>960</v>
+        <v>568</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>32</v>
+        <v>123</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>569</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H157" s="3" t="s">
-        <v>961</v>
-      </c>
-      <c r="I157" s="4" t="s">
-        <v>962</v>
+      <c r="H157" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="K157" s="3">
         <v>0</v>
@@ -14458,39 +14457,45 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.4">
-      <c r="A158" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="B158" s="3" t="s">
+    <row r="158" spans="1:12" s="5" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A158" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="B158" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C158" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="H158" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="I158" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="J158" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="K158" s="3">
-        <v>0</v>
-      </c>
-      <c r="L158" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="C158" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="I158" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="J158" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="K158" s="5">
+        <v>1</v>
+      </c>
+      <c r="L158" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3" t="s">
         <v>578</v>
       </c>
@@ -14498,22 +14503,10 @@
         <v>13</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="H159" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="I159" s="4" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="K159" s="3">
         <v>0</v>
@@ -14522,27 +14515,45 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A160" t="s">
+    <row r="160" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A160" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C160" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="E160" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="J160" t="s">
-        <v>594</v>
-      </c>
-      <c r="K160">
-        <v>2</v>
-      </c>
-      <c r="L160" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="F160" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="I160" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="J160" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="K160" s="3">
+        <v>0</v>
+      </c>
+      <c r="L160" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.4">
       <c r="A161" s="3" t="s">
         <v>578</v>
       </c>
@@ -14550,10 +14561,22 @@
         <v>13</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>595</v>
+        <v>584</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="H161" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="I161" s="4" t="s">
+        <v>587</v>
       </c>
       <c r="J161" s="3" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="K161" s="3">
         <v>0</v>
@@ -14562,7 +14585,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A162" s="3" t="s">
         <v>578</v>
       </c>
@@ -14570,10 +14593,22 @@
         <v>13</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>597</v>
+        <v>589</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="I162" s="4" t="s">
+        <v>592</v>
       </c>
       <c r="J162" s="3" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="K162" s="3">
         <v>0</v>
@@ -14582,24 +14617,24 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="3" t="s">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
         <v>578</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" t="s">
         <v>13</v>
       </c>
-      <c r="C163" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="J163" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="K163" s="3">
-        <v>0</v>
-      </c>
-      <c r="L163" s="3" t="s">
-        <v>28</v>
+      <c r="C163" t="s">
+        <v>582</v>
+      </c>
+      <c r="J163" t="s">
+        <v>594</v>
+      </c>
+      <c r="K163">
+        <v>2</v>
+      </c>
+      <c r="L163" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="164" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -14610,10 +14645,10 @@
         <v>13</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="J164" s="3" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="K164" s="3">
         <v>0</v>
@@ -14622,24 +14657,24 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="5" t="s">
+    <row r="165" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A165" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B165" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="J165" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="K165" s="5">
-        <v>1</v>
-      </c>
-      <c r="L165" s="5" t="s">
-        <v>57</v>
+      <c r="B165" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="J165" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="K165" s="3">
+        <v>0</v>
+      </c>
+      <c r="L165" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="166" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -14650,10 +14685,10 @@
         <v>13</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="J166" s="3" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="K166" s="3">
         <v>0</v>
@@ -14662,109 +14697,64 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="B167" s="2" t="s">
+    <row r="167" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B167" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C167" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G167" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H167" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="J167" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="K167" s="2">
-        <v>6</v>
-      </c>
-      <c r="L167" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="B168" s="2" t="s">
+      <c r="C167" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="J167" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="K167" s="3">
+        <v>0</v>
+      </c>
+      <c r="L167" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A168" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="J168" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="K168" s="5">
+        <v>1</v>
+      </c>
+      <c r="L168" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A169" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B169" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C168" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G168" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H168" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="J168" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="K168" s="2">
-        <v>1</v>
-      </c>
-      <c r="L168" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="F169" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G169" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H169" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="J169" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="K169" s="2">
+      <c r="C169" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="J169" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="K169" s="3">
         <v>0</v>
       </c>
-      <c r="L169" s="2" t="s">
-        <v>16</v>
+      <c r="L169" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="170" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
@@ -14775,10 +14765,10 @@
         <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>430</v>
+        <v>353</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>609</v>
@@ -14790,19 +14780,19 @@
         <v>32</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>431</v>
+        <v>354</v>
       </c>
       <c r="K170" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L170" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="171" spans="1:12" s="2" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A171" s="2" t="s">
         <v>607</v>
       </c>
@@ -14810,48 +14800,45 @@
         <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>355</v>
+        <v>428</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>975</v>
+        <v>611</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="F171" s="11" t="s">
-        <v>803</v>
+      <c r="F171" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="I171" s="11" t="s">
-        <v>889</v>
+        <v>612</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>356</v>
+        <v>429</v>
       </c>
       <c r="K171" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L171" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="172" spans="1:12" s="2" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A172" s="2" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>353</v>
+        <v>613</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>932</v>
+        <v>614</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>609</v>
@@ -14863,57 +14850,51 @@
         <v>32</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>933</v>
-      </c>
-      <c r="I172" s="11" t="s">
-        <v>934</v>
+        <v>615</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>354</v>
+        <v>616</v>
       </c>
       <c r="K172" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L172" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A173" t="s">
-        <v>619</v>
-      </c>
-      <c r="B173" t="s">
+    <row r="173" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A173" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C173" t="s">
-        <v>418</v>
-      </c>
-      <c r="D173" t="s">
-        <v>841</v>
-      </c>
-      <c r="E173" t="s">
-        <v>434</v>
-      </c>
-      <c r="F173" t="s">
-        <v>32</v>
-      </c>
-      <c r="G173" t="s">
-        <v>32</v>
-      </c>
-      <c r="H173" s="1" t="s">
-        <v>934</v>
-      </c>
-      <c r="I173" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="J173" t="s">
-        <v>419</v>
-      </c>
-      <c r="K173">
-        <v>4</v>
-      </c>
-      <c r="L173" t="s">
-        <v>43</v>
+      <c r="C173" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="K173" s="2">
+        <v>3</v>
+      </c>
+      <c r="L173" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="174" spans="1:12" s="2" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
@@ -14924,13 +14905,13 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>936</v>
+        <v>908</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>434</v>
+        <v>609</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>32</v>
@@ -14939,71 +14920,74 @@
         <v>32</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>937</v>
+        <v>909</v>
       </c>
       <c r="I174" s="11" t="s">
-        <v>938</v>
+        <v>910</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="K174" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L174" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="175" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="2" t="s">
+    <row r="175" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A175" t="s">
         <v>619</v>
       </c>
-      <c r="B175" s="2" t="s">
+      <c r="B175" t="s">
         <v>13</v>
       </c>
-      <c r="C175" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G175" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H175" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="J175" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="K175" s="2">
-        <v>3</v>
-      </c>
-      <c r="L175" s="2" t="s">
-        <v>16</v>
+      <c r="C175" t="s">
+        <v>418</v>
+      </c>
+      <c r="D175" t="s">
+        <v>817</v>
+      </c>
+      <c r="E175" t="s">
+        <v>434</v>
+      </c>
+      <c r="F175" t="s">
+        <v>32</v>
+      </c>
+      <c r="G175" t="s">
+        <v>32</v>
+      </c>
+      <c r="H175" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="J175" t="s">
+        <v>419</v>
+      </c>
+      <c r="K175">
+        <v>4</v>
+      </c>
+      <c r="L175" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="176" spans="1:12" s="2" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A176" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>837</v>
+        <v>912</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>941</v>
+        <v>434</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>32</v>
@@ -15012,16 +14996,16 @@
         <v>32</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>942</v>
+        <v>913</v>
       </c>
       <c r="I176" s="11" t="s">
-        <v>943</v>
+        <v>914</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="K176" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L176" s="2" t="s">
         <v>16</v>
@@ -15029,19 +15013,19 @@
     </row>
     <row r="177" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A177" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>364</v>
+        <v>430</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>941</v>
+        <v>609</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>32</v>
@@ -15050,19 +15034,19 @@
         <v>32</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>945</v>
+        <v>916</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>365</v>
+        <v>431</v>
       </c>
       <c r="K177" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L177" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="178" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:12" s="2" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A178" s="2" t="s">
         <v>620</v>
       </c>
@@ -15070,13 +15054,13 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>621</v>
+        <v>353</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>946</v>
+        <v>813</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>941</v>
+        <v>917</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>32</v>
@@ -15085,13 +15069,16 @@
         <v>32</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>947</v>
+        <v>918</v>
+      </c>
+      <c r="I178" s="11" t="s">
+        <v>919</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>622</v>
+        <v>354</v>
       </c>
       <c r="K178" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L178" s="2" t="s">
         <v>16</v>
@@ -15105,13 +15092,13 @@
         <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>430</v>
+        <v>364</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>858</v>
+        <v>920</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>941</v>
+        <v>917</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>32</v>
@@ -15120,91 +15107,161 @@
         <v>32</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>948</v>
+        <v>921</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>431</v>
+        <v>365</v>
       </c>
       <c r="K179" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L179" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A180" t="s">
+    <row r="180" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A180" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="J180" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="K180" s="2">
+        <v>0</v>
+      </c>
+      <c r="L180" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A181" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="J181" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="K181" s="2">
+        <v>3</v>
+      </c>
+      <c r="L181" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A182" t="s">
         <v>623</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B182" t="s">
         <v>13</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C182" t="s">
         <v>624</v>
       </c>
-      <c r="D180" t="s">
-        <v>949</v>
-      </c>
-      <c r="E180" t="s">
+      <c r="D182" t="s">
+        <v>925</v>
+      </c>
+      <c r="E182" t="s">
         <v>293</v>
       </c>
-      <c r="F180" t="s">
-        <v>32</v>
-      </c>
-      <c r="G180" t="s">
-        <v>32</v>
-      </c>
-      <c r="H180" t="s">
-        <v>950</v>
-      </c>
-      <c r="I180" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="J180" t="s">
+      <c r="F182" t="s">
+        <v>32</v>
+      </c>
+      <c r="G182" t="s">
+        <v>32</v>
+      </c>
+      <c r="H182" t="s">
+        <v>926</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="J182" t="s">
         <v>625</v>
       </c>
-      <c r="K180">
+      <c r="K182">
         <v>3</v>
       </c>
-      <c r="L180" t="s">
+      <c r="L182" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="181" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A181" s="3" t="s">
+    <row r="183" spans="1:12" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A183" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="B183" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C181" s="3" t="s">
+      <c r="C183" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="D181" s="3" t="s">
-        <v>952</v>
-      </c>
-      <c r="E181" s="3" t="s">
-        <v>953</v>
-      </c>
-      <c r="F181" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G181" s="3" t="s">
-        <v>954</v>
-      </c>
-      <c r="H181" s="3" t="s">
-        <v>955</v>
-      </c>
-      <c r="I181" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="J181" s="3" t="s">
+      <c r="D183" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="H183" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="I183" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="J183" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="K181" s="3">
+      <c r="K183" s="3">
         <v>0</v>
       </c>
-      <c r="L181" s="3" t="s">
+      <c r="L183" s="3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -15216,9 +15273,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4372B9AC-F2D7-42D8-8DB1-480F6DEA7ED9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E153DC6-AD20-497D-9181-32C1C655C92C}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34.25" bestFit="1" customWidth="1"/>
@@ -15292,7 +15349,7 @@
         <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -15360,7 +15417,7 @@
         <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -15411,7 +15468,7 @@
         <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -15496,7 +15553,7 @@
         <v>83</v>
       </c>
       <c r="G15" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
@@ -15530,7 +15587,7 @@
         <v>83</v>
       </c>
       <c r="G17" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
@@ -15581,7 +15638,7 @@
         <v>120</v>
       </c>
       <c r="G20" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
@@ -15683,7 +15740,7 @@
         <v>120</v>
       </c>
       <c r="G26" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
@@ -15734,7 +15791,7 @@
         <v>120</v>
       </c>
       <c r="G29" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
@@ -15768,7 +15825,7 @@
         <v>120</v>
       </c>
       <c r="G31" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
@@ -15836,7 +15893,7 @@
         <v>120</v>
       </c>
       <c r="G35" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
@@ -15938,7 +15995,7 @@
         <v>120</v>
       </c>
       <c r="G41" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
@@ -16275,10 +16332,10 @@
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G61" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
@@ -16292,10 +16349,10 @@
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G62" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
@@ -16309,10 +16366,10 @@
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G63" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
@@ -16326,10 +16383,10 @@
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G64" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
@@ -16343,10 +16400,10 @@
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G65" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
@@ -16360,7 +16417,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G66" t="s">
         <v>49</v>
@@ -16377,7 +16434,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G67" t="s">
         <v>83</v>
@@ -16394,10 +16451,10 @@
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G68" t="s">
-        <v>964</v>
+        <v>940</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.4">
@@ -16414,10 +16471,10 @@
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G69" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.4">
@@ -16434,10 +16491,10 @@
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G70" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.4">
@@ -16454,10 +16511,10 @@
         <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G71" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.4">
@@ -16474,10 +16531,10 @@
         <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G72" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.4">
@@ -16494,10 +16551,10 @@
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="G73" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.4">
@@ -16511,7 +16568,7 @@
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="G74" t="s">
         <v>120</v>
@@ -16528,10 +16585,10 @@
         <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="G75" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.4">
@@ -16545,7 +16602,7 @@
         <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="G76" t="s">
         <v>120</v>
@@ -16562,10 +16619,10 @@
         <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="G77" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.4">
@@ -16579,10 +16636,10 @@
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G78" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.4">
@@ -16596,10 +16653,10 @@
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G79" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.4">
@@ -16613,10 +16670,10 @@
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G80" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.4">
@@ -16630,10 +16687,10 @@
         <v>1</v>
       </c>
       <c r="F81" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G81" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.4">
@@ -16647,10 +16704,10 @@
         <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G82" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.4">
@@ -16664,10 +16721,10 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G83" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.4">
@@ -16681,10 +16738,10 @@
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G84" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.4">
@@ -16698,10 +16755,10 @@
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G85" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.4">
@@ -16715,10 +16772,10 @@
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G86" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.4">
@@ -16732,10 +16789,10 @@
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G87" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.4">
@@ -16749,10 +16806,10 @@
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G88" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.4">
@@ -16766,10 +16823,10 @@
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G89" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.4">
@@ -16783,10 +16840,10 @@
         <v>5</v>
       </c>
       <c r="F90" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G90" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.4">
@@ -16800,10 +16857,10 @@
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G91" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.4">
@@ -16817,10 +16874,10 @@
         <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="G92" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.4">
@@ -16834,10 +16891,10 @@
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="G93" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.4">
@@ -16851,10 +16908,10 @@
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="G94" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.4">
@@ -16868,10 +16925,10 @@
         <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="G95" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.4">
@@ -16905,7 +16962,7 @@
         <v>556</v>
       </c>
       <c r="G97" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.4">
@@ -16922,7 +16979,7 @@
         <v>556</v>
       </c>
       <c r="G98" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.4">
@@ -16939,7 +16996,7 @@
         <v>556</v>
       </c>
       <c r="G99" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.4">
@@ -16990,7 +17047,7 @@
         <v>578</v>
       </c>
       <c r="G102" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.4">
@@ -17075,11 +17132,45 @@
         <v>623</v>
       </c>
       <c r="G107" t="s">
-        <v>967</v>
+        <v>943</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>624</v>
+      </c>
+      <c r="C108" t="s">
+        <v>949</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+      <c r="F108" t="s">
+        <v>623</v>
+      </c>
+      <c r="G108" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>624</v>
+      </c>
+      <c r="C109" t="s">
+        <v>955</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+      <c r="F109" t="s">
+        <v>623</v>
+      </c>
+      <c r="G109" t="s">
+        <v>944</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{4372B9AC-F2D7-42D8-8DB1-480F6DEA7ED9}"/>
+  <autoFilter ref="A1:I1" xr:uid="{1E153DC6-AD20-497D-9181-32C1C655C92C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Analyzer解析管理.xlsx
+++ b/Analyzer解析管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://b0aa600df9934664bf4b-my.sharepoint.com/personal/masaharu_itou_ab_east_ntt_co_jp/Documents/ドキュメント/GitHub/SOSDB_Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="359477" documentId="8_{F7BFCF04-A82A-4CEF-B166-E6043107DC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48C69E63-9834-45AE-8910-B92F222EF19F}"/>
+  <xr:revisionPtr revIDLastSave="359479" documentId="8_{F7BFCF04-A82A-4CEF-B166-E6043107DC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CAC254D-C8C6-4CA7-8593-B06EAE19F5E2}"/>
   <bookViews>
-    <workbookView xWindow="6465" yWindow="570" windowWidth="19395" windowHeight="14145" tabRatio="686" firstSheet="3" activeTab="4" xr2:uid="{9A52E20E-468D-4D4B-A7CD-66A9B60B5C6C}"/>
+    <workbookView xWindow="975" yWindow="975" windowWidth="24000" windowHeight="12000" tabRatio="686" firstSheet="3" activeTab="4" xr2:uid="{9A52E20E-468D-4D4B-A7CD-66A9B60B5C6C}"/>
   </bookViews>
   <sheets>
     <sheet name="PathChartTree" sheetId="5" r:id="rId1"/>
@@ -4056,119 +4056,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
